--- a/docs/timeline_petcare2.xlsx
+++ b/docs/timeline_petcare2.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Timeline Dự án" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chú thích màu sắc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phân công module" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FSM &amp; Rules" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline Dự án" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chú thích màu sắc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phân công module" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FSM &amp; Rules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Timeline Dự án'!$A$4:$J$67</definedName>
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +72,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +156,24 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -171,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,6 +358,26 @@
     <xf numFmtId="164" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -773,19 +815,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -853,6 +897,16 @@
           <t>Tiến độ (%)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tiến độ FE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Chi tiết FE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -879,9 +933,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -894,8 +948,10 @@
           <t>M00: Setup</t>
         </is>
       </c>
-      <c r="J5" s="7" t="n">
-        <v>0</v>
+      <c r="J5" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -923,9 +979,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -938,8 +994,10 @@
           <t>M00: Setup</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n">
-        <v>0</v>
+      <c r="J6" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -967,9 +1025,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -982,8 +1040,10 @@
           <t>M02: IAM</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n">
-        <v>0</v>
+      <c r="J7" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1011,9 +1071,9 @@
           <t>BE-2 (Backend)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1026,8 +1086,10 @@
           <t>M00: Setup</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n">
-        <v>0</v>
+      <c r="J8" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1055,9 +1117,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1070,8 +1132,10 @@
           <t>M01: Auth + OTP</t>
         </is>
       </c>
-      <c r="J9" s="11" t="n">
-        <v>0</v>
+      <c r="J9" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1099,9 +1163,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1114,8 +1178,10 @@
           <t>M01: Auth + OTP</t>
         </is>
       </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
+      <c r="J10" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1143,9 +1209,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1158,8 +1224,10 @@
           <t>M02: IAM</t>
         </is>
       </c>
-      <c r="J11" s="11" t="n">
-        <v>0</v>
+      <c r="J11" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1187,9 +1255,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G12" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1202,8 +1270,10 @@
           <t>M03: Org &amp; Store</t>
         </is>
       </c>
-      <c r="J12" s="11" t="n">
-        <v>0</v>
+      <c r="J12" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1231,9 +1301,9 @@
           <t>BE-1 (Backend)</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1246,8 +1316,10 @@
           <t>M03: Org &amp; Store</t>
         </is>
       </c>
-      <c r="J13" s="11" t="n">
-        <v>0</v>
+      <c r="J13" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1495,9 +1567,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G19" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1510,8 +1582,15 @@
           <t>M00: Setup FE</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n">
-        <v>0</v>
+      <c r="J19" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L19" s="60" t="inlineStr">
+        <is>
+          <t>Vite + React + Tailwind + TanStack Query + Auth Context + Layout. Dev server chạy mượt.</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1539,9 +1618,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G20" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1554,8 +1633,15 @@
           <t>M01: Auth (FE)</t>
         </is>
       </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
+      <c r="J20" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L20" s="60" t="inlineStr">
+        <is>
+          <t>Login/Register/OTP kết nối API thật + JWT + Route Guard</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1935,9 +2021,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G29" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -1950,8 +2036,15 @@
           <t>M04: Pet (FE)</t>
         </is>
       </c>
-      <c r="J29" s="15" t="n">
-        <v>0</v>
+      <c r="J29" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L29" s="60" t="inlineStr">
+        <is>
+          <t>Pets CRUD + EMR tabs + Caregivers UI + Store (16 screens B2C)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1979,9 +2072,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G30" s="58" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -1994,8 +2087,15 @@
           <t>M05: Catalog (FE)</t>
         </is>
       </c>
-      <c r="J30" s="15" t="n">
-        <v>0</v>
+      <c r="J30" s="59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L30" s="60" t="inlineStr">
+        <is>
+          <t>Shop/Cart/Checkout + Recommend + Hotel/News/About + Packages/Orders</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2375,9 +2475,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G39" s="61" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
@@ -2390,8 +2490,15 @@
           <t>M06: Appointment (FE)</t>
         </is>
       </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
+      <c r="J39" s="62" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="L39" s="60" t="inlineStr">
+        <is>
+          <t>Booking 4-step UI xong, đang nối API Appointment slot realtime</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2419,9 +2526,9 @@
           <t>FE-1 (Frontend)</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
+      <c r="G40" s="61" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -2434,8 +2541,15 @@
           <t>M14: Order (FE)</t>
         </is>
       </c>
-      <c r="J40" s="19" t="n">
-        <v>0</v>
+      <c r="J40" s="62" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L40" s="60" t="inlineStr">
+        <is>
+          <t>Checkout + VNPAY sandbox UI xong, cần test thật</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2830,8 +2944,15 @@
           <t>M09: Clinical (FE)</t>
         </is>
       </c>
-      <c r="J49" s="23" t="n">
-        <v>0</v>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L49" s="60" t="inlineStr">
+        <is>
+          <t>Chờ BE-2 xong Clinical API</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -2874,8 +2995,15 @@
           <t>M15+17 (FE)</t>
         </is>
       </c>
-      <c r="J50" s="23" t="n">
-        <v>0</v>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L50" s="60" t="inlineStr">
+        <is>
+          <t>Chờ BE-1 xong Invoice/Refund API</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3624,6 +3752,1152 @@
       </c>
       <c r="J67" s="35" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FE Customer: Dashboard + Navigation Header/Footer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F68" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G68" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Public layout hoàn chỉnh</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>M00: Setup FE</t>
+        </is>
+      </c>
+      <c r="J68" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Header/Footer public, search popover, notification bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FE Customer: Trang chủ Hero Mascot GSAP + Recommend</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F69" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G69" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Home page tương tác</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>M04: Pet (FE)</t>
+        </is>
+      </c>
+      <c r="J69" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mascot theo chuột, boop interaction, 3 service cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FE Customer: Hotel/News/About pages</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F70" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G70" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Static pages</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>M04: Pet (FE)</t>
+        </is>
+      </c>
+      <c r="J70" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bảng giá khách sạn, bài cẩm nang</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FE Customer: Shop + Cart + Checkout</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F71" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G71" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>E-commerce UI</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>M05: Catalog (FE)</t>
+        </is>
+      </c>
+      <c r="J71" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Grid sản phẩm, bộ lọc, cart Zustand, checkout form</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FE Admin: Layout + RBAC Sidebar + Header</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F72" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G72" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Admin core framework</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>M00: Admin Core</t>
+        </is>
+      </c>
+      <c r="J72" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Sidebar co giãn, 8 roles, route guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FE Admin: Login Admin (/admin/login)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="F73" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G73" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Admin auth</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>M01: Auth (FE)</t>
+        </is>
+      </c>
+      <c r="J73" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Linear/Awwwards style, switch role 1 chạm</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FE Admin: Reception POS + Queue</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F74" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G74" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Reception UI</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>M07: Walk-in (FE)</t>
+        </is>
+      </c>
+      <c r="J74" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Check-in, FIFO walk-in, gọi số TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FE Admin: Vet EMR + Vaccination</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F75" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G75" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Vet UI</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>M09: Clinical (FE)</t>
+        </is>
+      </c>
+      <c r="J75" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Hàng đợi, form khám, kê đơn, vaccine</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FE Admin: Grooming Kanban + Refunds Maker-Checker</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F76" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G76" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Spa + Finance UI</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>M11+M17 (FE)</t>
+        </is>
+      </c>
+      <c r="J76" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Kanban spa, duyệt hoàn tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>W2: Core Domain (17-21/09)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FE Admin: Warehouse + Workforce + Dashboard</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F77" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G77" s="64" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Inventory/Reports UI</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>M12+M08 (FE)</t>
+        </is>
+      </c>
+      <c r="J77" s="64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Tồn kho, phân ca, dashboard doanh thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>W3: Commerce P1 (24-28/09)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>FE: Nối API Appointments + slot realtime</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F78" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G78" s="65" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>API integration</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>M06: Appointment (FE)</t>
+        </is>
+      </c>
+      <c r="J78" s="65" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>UI xong, đang kết nối BE-1 API</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>W3: Commerce P1 (24-28/09)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FE: Nối API Orders + VNPAY sandbox</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F79" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G79" s="65" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Payment integration</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>M14: Order (FE)</t>
+        </is>
+      </c>
+      <c r="J79" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Checkout UI xong, đang test VNPAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>W3: Commerce P1 (24-28/09)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>FE: Nối API Customer B2C (Pets/Cart/Vouchers)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F80" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G80" s="65" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Customer APIs</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>M04+M05 (FE)</t>
+        </is>
+      </c>
+      <c r="J80" s="65" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>UI xong, đang nối BE-2 APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>W4: Commerce P2 (01-05/10)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FE: Nối API Clinical EMR + Consent</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F81" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G81" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>EMR integration</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>M09: Clinical (FE)</t>
+        </is>
+      </c>
+      <c r="J81" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Chờ BE-2 xong Consent + EMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>W4: Commerce P2 (01-05/10)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FE: Nối API Invoices + Refunds Maker-Checker</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F82" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G82" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Finance APIs</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>M15+M17 (FE)</t>
+        </is>
+      </c>
+      <c r="J82" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Chờ BE-1 xong Invoice/Refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>W5: Integration (08-12/10)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FE: Nối API Workforce + Reports Dashboard</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F83" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G83" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Admin reports</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>M08+M24 (FE)</t>
+        </is>
+      </c>
+      <c r="J83" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Chờ BE-2 xong Reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>W5: Integration (08-12/10)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FE: SSE Notifications realtime + Mobile responsive</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F84" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G84" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>M23: Notification (FE)</t>
+        </is>
+      </c>
+      <c r="J84" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Chờ BE-1 xong Notification SSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>W6: Polish (15-17/10)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FE: E2E error handling (401/403 auto logout)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F85" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G85" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>M00: Polish FE</t>
+        </is>
+      </c>
+      <c r="J85" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Toàn hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>W6: Polish (15-17/10)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FE: Demo rehearsal + kịch bản 4 vai</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F86" s="63" t="inlineStr">
+        <is>
+          <t>FE-1 (Frontend)</t>
+        </is>
+      </c>
+      <c r="G86" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Demo prep</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>M00: Demo</t>
+        </is>
+      </c>
+      <c r="J86" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Phối hợp 3 người</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Demo (18-19/10)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FE: Tổng duyệt Demo Live</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Cả nhóm</t>
+        </is>
+      </c>
+      <c r="G87" s="66" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Milestone M4</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>M00: Demo</t>
+        </is>
+      </c>
+      <c r="J87" s="65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Demo 4 vai: Khách-&gt;Tiếp tân-&gt;Bác sĩ-&gt;Quản lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="67">
+        <f>== TOM TAT TIEN DO FE (21/09/2026) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tong FE tasks moi (W2-W6):</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Da hoan thanh:</t>
+        </is>
+      </c>
+      <c r="B97" s="64" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Dang lam:</t>
+        </is>
+      </c>
+      <c r="B98" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Chua bat dau:</t>
+        </is>
+      </c>
+      <c r="B99" s="66" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3801,7 +5075,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
         <is>
@@ -3857,7 +5130,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
         <is>
